--- a/MSGraphAPI_Endpoints.xlsx
+++ b/MSGraphAPI_Endpoints.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\dafsaw302029910.msad.crbgf.net\dpa_rpa_fileshare\rpa_aa\RS\HealthCheckup\MSGraphAPI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FD91D16-70E9-47DF-9109-8B884774ACAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67FDE46E-0C85-4B3C-8BB5-8F672750378A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{50F37EE4-1E82-4AF5-AD6D-7C88DE71EAB8}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="Dev" sheetId="2" r:id="rId2"/>
+    <sheet name="UAT" sheetId="3" r:id="rId3"/>
+    <sheet name="Prod" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Dev!$A$2:$B$20</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="67">
   <si>
     <t>MSGraphAPITokenURI</t>
   </si>
@@ -53,9 +59,6 @@
     <t>MSGraphAPIReadEmailURI</t>
   </si>
   <si>
-    <t xml:space="preserve"> https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/mailFolders/Inbox/messages?$filter=subject eq '&lt;FilterSubject&gt;' and contains(from/emailAddress/address, '&lt;FilterFromAddress&gt;') and  hasAttachments eq true &amp; $select=Body</t>
-  </si>
-  <si>
     <t>MSGraphAPIEmailMessageIDURI</t>
   </si>
   <si>
@@ -89,59 +92,164 @@
     <t xml:space="preserve"> https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/messages</t>
   </si>
   <si>
-    <t>MSGraphAPISaveSentEmailURI</t>
-  </si>
-  <si>
-    <t>https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/mailFolders/SentItems/messages?$filter=singleValueExtendedProperties/any(ep:ep/id eq 'String {&lt;Property-GUID&gt;} Name TrackingID' and ep/value eq '&lt;UniqueID&gt;')</t>
-  </si>
-  <si>
-    <t>MSGraphAPIGetMIMEURI</t>
-  </si>
-  <si>
     <t>https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/messages/&lt;MessageID&gt;/$value</t>
   </si>
   <si>
-    <t>MSGraphAPIReplyReadEmailURI</t>
-  </si>
-  <si>
-    <t>https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/mailFolders/Inbox/messages?$filter=subject eq '&lt;EmailSubject&gt;' and contains(from/emailAddress/address,'&lt;SenderEmailAddress&gt;') &amp; $select=id,subject,receivedDateTime,sender&amp;$top=100</t>
-  </si>
-  <si>
-    <t>MSGraphAPIReplyTextURI</t>
-  </si>
-  <si>
     <t>https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/messages/&lt;MessageID&gt;/reply</t>
   </si>
   <si>
-    <t>MSGraphAPIReplyAllTextURI</t>
-  </si>
-  <si>
     <t>https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/messages/&lt;MessageID&gt;/replyAll</t>
   </si>
   <si>
-    <t>MSGraphAPIReplyHTMLURI</t>
-  </si>
-  <si>
-    <t>https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/messages/&lt;MessageID&gt;/createReply</t>
-  </si>
-  <si>
-    <t>MSGraphAPIReplyAllHTMLURI</t>
-  </si>
-  <si>
-    <t>https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/messages/&lt;MessageID&gt;/createReplyAll</t>
-  </si>
-  <si>
     <t>MSGraph API Endpoints</t>
   </si>
   <si>
     <t>Scenario</t>
+  </si>
+  <si>
+    <t>https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/mailFolders/Inbox/messages?$filter=subject eq '&lt;FilterSubject&gt;' and contains(from/emailAddress/address, '&lt;FilterFromAddress&gt;')</t>
+  </si>
+  <si>
+    <t>Changes</t>
+  </si>
+  <si>
+    <t>Email Action</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Send Email</t>
+  </si>
+  <si>
+    <t>https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/mailFolders/SentItems/messages?$filter=singleValueExtendedProperties/any(ep:ep/id eq 'String {66f5a359-4659-4830-9070-00040ec6ac6e} Name TrackingID' and ep/value eq '&lt;UniqueID&gt;')</t>
+  </si>
+  <si>
+    <t>MSGraphAPIGetSentItemsURI</t>
+  </si>
+  <si>
+    <t>MSGraphAPIGetMIMEValueURI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is used to get the sent item email </t>
+  </si>
+  <si>
+    <t>ReadEmail</t>
+  </si>
+  <si>
+    <t>To find the undelivered email</t>
+  </si>
+  <si>
+    <t>Retrieve the email as MIME content and save email as .eml file</t>
+  </si>
+  <si>
+    <t>MSGraphAPIReadSubFolderEmailURI</t>
+  </si>
+  <si>
+    <t>Read email from sub folders</t>
+  </si>
+  <si>
+    <t>MSGraphAPIFilterEmailBySubjectURI</t>
+  </si>
+  <si>
+    <t>Reply</t>
+  </si>
+  <si>
+    <t>https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/mailFolders/Inbox/messages?$filter=subject eq '&lt;FilterSubject&gt;'  and contains(from/emailAddress/address, '&lt;FilterFromAddress&gt;') and receivedDateTime ge &lt;EmailReceivedDate&gt;T00:00:00Z and receivedDateTime le &lt;EmailReceivedDate&gt;T23:59:59Z</t>
+  </si>
+  <si>
+    <t>MSGraphAPIFilterReplyURI</t>
+  </si>
+  <si>
+    <t>https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/mailFolders/Inbox/messages?$filter=conversationId eq '&lt;ConversationID&gt;'</t>
+  </si>
+  <si>
+    <t>MSGraphAPIReplyURI</t>
+  </si>
+  <si>
+    <t>MSGraphAPIReplyAllURI</t>
+  </si>
+  <si>
+    <t>MSGraphAPIGetConversationURI</t>
+  </si>
+  <si>
+    <t>Forward</t>
+  </si>
+  <si>
+    <t>https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/mailFolders/SentItems/messages?$filter=subject eq '&lt;FilterSubject&gt;' and sentDateTime ge &lt;EmailSentDate&gt;T00:00:00Z and sentDateTime le &lt;EmailSentDate&gt;T23:59:59Z</t>
+  </si>
+  <si>
+    <t>MSGraphAPIFilterForwardURI</t>
+  </si>
+  <si>
+    <t>MSGraphAPIForwardURI</t>
+  </si>
+  <si>
+    <t>https://login.microsoftonline.com/&lt;TenantID&gt;/oauth2/v2.0/token</t>
+  </si>
+  <si>
+    <t>https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/sendMail</t>
+  </si>
+  <si>
+    <t>https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/messages/&lt;MessageID&gt;/attachments</t>
+  </si>
+  <si>
+    <t>https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/messages/&lt;MessageID&gt;/move</t>
+  </si>
+  <si>
+    <t>https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/mailFolders</t>
+  </si>
+  <si>
+    <t>https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/messages</t>
+  </si>
+  <si>
+    <t>Draft</t>
+  </si>
+  <si>
+    <t>Move</t>
+  </si>
+  <si>
+    <t>https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/messages/&lt;MessageID&gt;/createForward</t>
+  </si>
+  <si>
+    <t>https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/messages/&lt;DraftMessageID&gt;/send</t>
+  </si>
+  <si>
+    <t>https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/messages/&lt;DraftMessageID&gt;</t>
+  </si>
+  <si>
+    <t>MSGraphAPIDraftURI</t>
+  </si>
+  <si>
+    <t>MSGraphAPIDraftSendURI</t>
+  </si>
+  <si>
+    <t>https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/mailFolders/Inbox/messages?$filter=subject eq '&lt;FilterSubject&gt;' and contains(from/emailAddress/address,'&lt;FilterFromAddress&gt;') and hasAttachments eq true and isRead eq false&amp; $select=id,subject &amp; $top=1</t>
+  </si>
+  <si>
+    <t>https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/mailFolders/inbox/messages?$filter=contains(subject,'&lt;FilterSubject&gt;') and isRead eq false</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/mailFolders/Inbox/messages?$filter=subject eq '&lt;FilterSubject&gt;' and contains(from/emailAddress/address, '&lt;FilterFromAddress&gt;') and hasAttachments eq true and isRead eq false&amp; $select=id, subject &amp; $top=1</t>
+  </si>
+  <si>
+    <t>https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/mailFolders/Inbox/messages?$filter=subject eq '&lt;FilterSubject&gt;' and contains(from/emailAddress/address, '&lt;FilterFromAddress&gt;') and isRead eq false</t>
+  </si>
+  <si>
+    <t>https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/mailFolders/&lt;DestinationID&gt;/messages?$filter=subject eq '&lt;FilterSubject&gt;' and contains(from/emailAddress/address,'&lt;FilterFromAddress&gt;') and isRead eq false</t>
+  </si>
+  <si>
+    <t>https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/mailFolders/&lt;DestinationID&gt;/messages?$filter=subject eq '&lt;FilterSubject&gt;' and contains(from/emailAddress/address,'&lt;FilterFromAddress&gt;') and receivedDateTime ge &lt;EmailReceivedDate&gt;T00:00:00Z and receivedDateTime le &lt;EmailReceivedDate&gt;T23:59:59Z</t>
+  </si>
+  <si>
+    <t>MSGraphAPIMoveFilterEmailURI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,16 +257,50 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA100FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -166,18 +308,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFA100FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -506,159 +682,838 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECBDEF07-8AC2-42F4-A6EC-50EBB674AE2A}">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="201.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="201.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="151.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="6"/>
+    </row>
+    <row r="4" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="6"/>
+    </row>
+    <row r="6" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="6"/>
+    </row>
+    <row r="7" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="6"/>
+    </row>
+    <row r="8" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="6"/>
+    </row>
+    <row r="9" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="6"/>
+    </row>
+    <row r="11" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="17" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="1"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="1"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="1"/>
+    </row>
+    <row r="27" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D4" r:id="rId1" xr:uid="{61812607-F5BB-4BCE-AF3D-C6642BD5BECE}"/>
+    <hyperlink ref="C12" r:id="rId2" xr:uid="{D5BFED9F-E904-458E-A892-4A51FBAE8C13}"/>
+    <hyperlink ref="C13" r:id="rId3" xr:uid="{D53003B2-A304-4889-AFF3-9B816F1AD66E}"/>
+    <hyperlink ref="C14" r:id="rId4" xr:uid="{AC3A0F34-9E09-4734-83F5-169B9A52DCF8}"/>
+    <hyperlink ref="C15" r:id="rId5" xr:uid="{E00835A1-A562-4BFA-9778-E737F9AFD44C}"/>
+    <hyperlink ref="C17" r:id="rId6" display="https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/mailFolders/Inbox/messages?$filter=subject eq '&lt;FilterSubject&gt;'  and contains(from/emailAddress/address, '&lt;FilterFromAddress&gt;') and receivedDateTime ge &lt;EmailReceivedDate&gt;T00:00:00Z and receivedDateTime le &lt;EmailReceivedDate&gt;T23:59:59Z" xr:uid="{DA6BA3F8-BAAC-473E-B5EA-8D0A8DCC4DD7}"/>
+    <hyperlink ref="C18" r:id="rId7" xr:uid="{273EB3FF-68C4-4C87-96AF-BFB8B5FC75CF}"/>
+    <hyperlink ref="C19" r:id="rId8" xr:uid="{243CD852-4104-47A5-81E9-3F2435B36F08}"/>
+    <hyperlink ref="C20" r:id="rId9" xr:uid="{02691E40-8F0A-43B9-B870-6C0559C8AADB}"/>
+    <hyperlink ref="C22" r:id="rId10" xr:uid="{74716574-BAA8-4E8A-B499-7F2903EA7919}"/>
+    <hyperlink ref="D23" r:id="rId11" xr:uid="{B5F67B2E-AED1-4E46-8EF2-0F2876631230}"/>
+    <hyperlink ref="C25" r:id="rId12" xr:uid="{4D491BAF-B90F-440A-8D60-EAF3BE467C95}"/>
+    <hyperlink ref="C24" r:id="rId13" xr:uid="{A3518404-8164-4B94-8C0E-EF5563118BC4}"/>
+    <hyperlink ref="C23" r:id="rId14" xr:uid="{EA379EAF-29E7-4121-B345-36168BE60835}"/>
+    <hyperlink ref="C4" r:id="rId15" xr:uid="{84D46D01-2286-4A69-AD56-EFEC28965172}"/>
+    <hyperlink ref="C27" r:id="rId16" display="https://graph.microsoft.com/v1.0/users/&lt;MailBoxID&gt;/mailFolders/&lt;DestinationID&gt;/messages?$filter=subject eq '&lt;FilterSubject&gt;' and contains(from/emailAddress/address,'&lt;FilterFromAddress&gt;') and receivedDateTime ge &lt;EmailReceivedDate&gt;T00:00:00Z and receivedDateTime le &lt;EmailReceivedDate&gt;T23:59:59Z" xr:uid="{1C0F702C-ED21-4E3C-A7C3-08DC48DC97B2}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{600F0FD4-3224-46B9-9B89-FBE9C66F00EF}">
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="249.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="215.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" t="s">
-        <v>31</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E43D420D-AF50-4AC9-99B0-52980571D8B8}">
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="249.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>1</v>
+      <c r="B1" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{440CBF63-C105-47AD-A43D-904E8C25C8FD}">
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="249.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>3</v>
+      <c r="B2" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B4" s="1" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="B5" s="1" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
+      <c r="A9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="A10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B11" t="s">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" t="s">
-        <v>28</v>
-      </c>
-    </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" t="s">
-        <v>30</v>
+      <c r="A17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B12" r:id="rId1" xr:uid="{26BD2E35-5A58-403D-800D-70322A1C6A5E}"/>
-    <hyperlink ref="B11" r:id="rId2" xr:uid="{6B00C5BF-2412-400D-8AD3-8FB3D7388A0C}"/>
-    <hyperlink ref="B13" r:id="rId3" xr:uid="{739D1719-B860-4412-AC29-0C35EF8950A7}"/>
-    <hyperlink ref="B14" r:id="rId4" xr:uid="{EC87801F-DDD2-41A0-A89F-D2D0E35C7AAB}"/>
-    <hyperlink ref="B15" r:id="rId5" xr:uid="{EC235A12-E77D-4C38-A4F1-3B8F2CC27D3B}"/>
-    <hyperlink ref="B16" r:id="rId6" xr:uid="{5986DB06-187D-416C-8DCD-7FF0026C5ACC}"/>
-    <hyperlink ref="B17" r:id="rId7" xr:uid="{80D360A2-0F06-4983-AB66-EAD5C88283E3}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>